--- a/majors/DataSheet.xlsx
+++ b/majors/DataSheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/majors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="6_{F16F1FBA-C992-4824-B99B-6423D52E8D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52503350-3E6C-469B-AA5D-8698F75B73CB}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="6_{F16F1FBA-C992-4824-B99B-6423D52E8D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BE1C2E1-35F8-465B-9F9B-61CD65268554}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="13" activeTab="17" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>

--- a/majors/DataSheet.xlsx
+++ b/majors/DataSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/majors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="6_{F16F1FBA-C992-4824-B99B-6423D52E8D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BE1C2E1-35F8-465B-9F9B-61CD65268554}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="6_{F16F1FBA-C992-4824-B99B-6423D52E8D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE00D7E1-3457-40DD-B7FD-484967EDFEE7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="13" activeTab="17" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -2078,7 +2078,7 @@
     <t>wm$qY@09</t>
   </si>
   <si>
-    <t>https://n9971009:wm$qY@09@stage-underwritingplatform.grsazr.lmig.com</t>
+    <t>https://n9971009:wm$qY@09@test5-underwritingplatform.grsazr.lmig.com</t>
   </si>
 </sst>
 </file>
@@ -2521,6 +2521,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>

--- a/majors/DataSheet.xlsx
+++ b/majors/DataSheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/majors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="6_{F16F1FBA-C992-4824-B99B-6423D52E8D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE00D7E1-3457-40DD-B7FD-484967EDFEE7}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="6_{F16F1FBA-C992-4824-B99B-6423D52E8D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9B473AD-BAE2-4055-A94C-7A826B5EDF7D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="13" activeTab="17" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -2078,7 +2078,7 @@
     <t>wm$qY@09</t>
   </si>
   <si>
-    <t>https://n9971009:wm$qY@09@test5-underwritingplatform.grsazr.lmig.com</t>
+    <t>https://n9971009:wm$qY@09@stage-underwritingplatform.grsazr.lmig.com</t>
   </si>
 </sst>
 </file>

--- a/majors/DataSheet.xlsx
+++ b/majors/DataSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/majors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="6_{F16F1FBA-C992-4824-B99B-6423D52E8D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9B473AD-BAE2-4055-A94C-7A826B5EDF7D}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="6_{F16F1FBA-C992-4824-B99B-6423D52E8D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A275CDA7-BC3C-4085-A869-3EEE26C86F65}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="13" activeTab="17" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -2078,7 +2078,7 @@
     <t>wm$qY@09</t>
   </si>
   <si>
-    <t>https://n9971009:wm$qY@09@stage-underwritingplatform.grsazr.lmig.com</t>
+    <t>https://n9971009:wm$qY@09@hfstage-underwritingplatform.grsazr.lmig.com</t>
   </si>
 </sst>
 </file>

--- a/majors/DataSheet.xlsx
+++ b/majors/DataSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://libertymutual-my.sharepoint.com/personal/mohammad_talib_libertymutual_com/Documents/Desktop/regression-pack/majors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="6_{F16F1FBA-C992-4824-B99B-6423D52E8D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9B473AD-BAE2-4055-A94C-7A826B5EDF7D}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="6_{F16F1FBA-C992-4824-B99B-6423D52E8D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52BBCF85-621A-421D-BDC1-73CBFFB88829}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="13" activeTab="17" xr2:uid="{A2EF6AEE-92DE-49D8-BB60-1A120F6353A4}"/>
   </bookViews>
@@ -2078,7 +2078,7 @@
     <t>wm$qY@09</t>
   </si>
   <si>
-    <t>https://n9971009:wm$qY@09@stage-underwritingplatform.grsazr.lmig.com</t>
+    <t>https://n9971009:wm$qY@09@test-underwritingplatform.grsazr.lmig.com</t>
   </si>
 </sst>
 </file>
